--- a/APP_(Izmantojot_27.10.2025_lekcijas_kodu_as_template)/app/models/produkti.xlsx
+++ b/APP_(Izmantojot_27.10.2025_lekcijas_kodu_as_template)/app/models/produkti.xlsx
@@ -1,48 +1,222 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P35E\Downloads\8.01.2026\jaunie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12CA4CB6-3098-4A6C-B3C8-3D659540B620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BA425EF-BD09-4C55-A4BD-FCB7F950518B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2415" yWindow="1125" windowWidth="24765" windowHeight="13635" xr2:uid="{7A312AA4-6112-4573-8839-A00361382EFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Produktu saraksts:</t>
   </si>
   <si>
-    <t>Vistas fileja, Tītara fileja, Lasis, Menca, Olas, Biezpiens, Grieķu jogurts, Lēcas, Aunazirņi, Tofu, Auzu pārslas, Brūnie rīsi, Kvinoja, Griķi, Piens, Pilngraudu makaroni,Batāts, Kartupeļi, Bulgurs, Siers, Āboli, Banāni, Apelsīni, Mellenes, Zemenes, Avokado, Citroni, Bumbieri, Kivi, Vīnogas, Spināti, Brokoļi, Burkāni, Gurķi Tomāti, Paprika, Sīpoli, Ķiploki, Puķkāposti, Kabači, Salātlapas, Bietes, Selerijas, Zaļās pupiņas, Sēnes, Olīveļļa, Mandeles, Valrieksti, Čia sēklas, Linsēklas</t>
+    <t>Vistas fileja</t>
+  </si>
+  <si>
+    <t>Tītara fileja</t>
+  </si>
+  <si>
+    <t>Lasis</t>
+  </si>
+  <si>
+    <t>Menca</t>
+  </si>
+  <si>
+    <t>Olas</t>
+  </si>
+  <si>
+    <t>Biezpiens</t>
+  </si>
+  <si>
+    <t>Grieķu jogurts</t>
+  </si>
+  <si>
+    <t>Lēcas</t>
+  </si>
+  <si>
+    <t>Aunazirņi</t>
+  </si>
+  <si>
+    <t>Tofu</t>
+  </si>
+  <si>
+    <t>Auzu pārslas</t>
+  </si>
+  <si>
+    <t>Brūnie rīsi</t>
+  </si>
+  <si>
+    <t>Kvinoja</t>
+  </si>
+  <si>
+    <t>Griķi</t>
+  </si>
+  <si>
+    <t>Piens</t>
+  </si>
+  <si>
+    <t>Kartupeļi</t>
+  </si>
+  <si>
+    <t>Bulgurs</t>
+  </si>
+  <si>
+    <t>Siers</t>
+  </si>
+  <si>
+    <t>Āboli</t>
+  </si>
+  <si>
+    <t>Banāni</t>
+  </si>
+  <si>
+    <t>Apelsīni</t>
+  </si>
+  <si>
+    <t>Mellenes</t>
+  </si>
+  <si>
+    <t>Zemenes</t>
+  </si>
+  <si>
+    <t>Avokado</t>
+  </si>
+  <si>
+    <t>Citroni</t>
+  </si>
+  <si>
+    <t>Bumbieri</t>
+  </si>
+  <si>
+    <t>Kivi</t>
+  </si>
+  <si>
+    <t>Vīnogas</t>
+  </si>
+  <si>
+    <t>Spināti</t>
+  </si>
+  <si>
+    <t>Brokoļi</t>
+  </si>
+  <si>
+    <t>Burkāni</t>
+  </si>
+  <si>
+    <t>Gurķi Tomāti</t>
+  </si>
+  <si>
+    <t>Paprika</t>
+  </si>
+  <si>
+    <t>Sīpoli</t>
+  </si>
+  <si>
+    <t>Ķiploki</t>
+  </si>
+  <si>
+    <t>Puķkāposti</t>
+  </si>
+  <si>
+    <t>Kabači</t>
+  </si>
+  <si>
+    <t>Salātlapas</t>
+  </si>
+  <si>
+    <t>Bietes</t>
+  </si>
+  <si>
+    <t>Selerijas</t>
+  </si>
+  <si>
+    <t>Zaļās pupiņas</t>
+  </si>
+  <si>
+    <t>Sēnes</t>
+  </si>
+  <si>
+    <t>Olīveļļa</t>
+  </si>
+  <si>
+    <t>Mandeles</t>
+  </si>
+  <si>
+    <t>Valrieksti</t>
+  </si>
+  <si>
+    <t>Čia sēklas</t>
+  </si>
+  <si>
+    <t>Linsēklas</t>
+  </si>
+  <si>
+    <t>Pilngraudu makaroni</t>
+  </si>
+  <si>
+    <t>Batāts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -63,15 +237,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Parasts" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{7F74CF83-09CA-4B6C-B6D5-244CE5B140E4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -87,56 +264,150 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -198,13 +469,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -213,6 +477,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -277,31 +548,292 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41ADEAFD-D302-4866-8BB3-7517FE3E41DF}">
+  <dimension ref="A1:A50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="260.42578125" customWidth="1"/>
-    <col min="2" max="2" width="113.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
